--- a/mappings/source_to_bronze/taxonomy.xlsx
+++ b/mappings/source_to_bronze/taxonomy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nason\Desktop\Projects\ActiveProjects\BlixHealth\mappings\source_to_bronze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9F0856-A2A6-4EE8-AA37-DB99CF5F1AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B3FF5C-2E13-4C71-B615-4C6633B57E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36405" yWindow="3585" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38505" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="22">
   <si>
     <t>source_database</t>
   </si>
@@ -82,6 +82,15 @@
   </si>
   <si>
     <t>Section</t>
+  </si>
+  <si>
+    <t>external</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>taxonomy</t>
   </si>
 </sst>
 </file>
@@ -105,7 +114,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -199,19 +208,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -228,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -236,9 +232,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -249,29 +244,29 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
         <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -550,14 +545,14 @@
     <tableColumn id="1" xr3:uid="{AD010FFD-DF57-4FB6-B606-2BF3C5F7531C}" name="source_database" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{192A1CE1-D3BC-4045-A423-5F4BC479257F}" name="source_schema" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{F295221E-BE62-4DDE-B2F7-C560970C4BA9}" name="source_table" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{ABF23023-FBC3-4EBE-A59A-90563B3FBA43}" name="source_field" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{843668BA-346A-424D-AC97-1BF5FABC488A}" name="target_database" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{3B5A1130-BFA0-4B44-AE79-7BE6C7363D9F}" name="target_schema" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{F5AE50A3-B96E-4679-AA62-A46503C731E2}" name="target_table" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{01E4E314-F140-45BF-B9F5-F8943C5E0067}" name="target_field" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{85D98F41-13D8-485C-9D59-A9DA5FF8A9F1}" name="sql_transform" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{28F6554B-37B6-484C-B756-D76B2C1A9A60}" name="python_transform" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{6993F87C-15D1-44F2-972E-DDBA4448307D}" name="lookup_table" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{ABF23023-FBC3-4EBE-A59A-90563B3FBA43}" name="source_field" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{843668BA-346A-424D-AC97-1BF5FABC488A}" name="target_database" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{3B5A1130-BFA0-4B44-AE79-7BE6C7363D9F}" name="target_schema" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{F5AE50A3-B96E-4679-AA62-A46503C731E2}" name="target_table" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{01E4E314-F140-45BF-B9F5-F8943C5E0067}" name="target_field" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{85D98F41-13D8-485C-9D59-A9DA5FF8A9F1}" name="sql_transform" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{28F6554B-37B6-484C-B756-D76B2C1A9A60}" name="python_transform" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{6993F87C-15D1-44F2-972E-DDBA4448307D}" name="lookup_table" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -878,10 +873,16 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="8" t="s">
+      <c r="A2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="5"/>
@@ -893,109 +894,151 @@
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8" t="s">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="9"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="8"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8" t="s">
+      <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8" t="s">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8" t="s">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="9"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="8"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8" t="s">
+      <c r="A7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="9"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8" t="s">
+      <c r="A8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="9"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8" t="s">
+      <c r="A9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="9"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
